--- a/public/fisiorock_block3.xlsx
+++ b/public/fisiorock_block3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U82739\Documents\Personale\FisioRock\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U82739\workspace\fisiorock-workouts\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A1C2F3-FFFA-44E7-AA6C-006EABB947CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA83248-7C4D-4BF4-A968-38D896548B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29550" yWindow="2310" windowWidth="21600" windowHeight="11835" activeTab="3" xr2:uid="{3CC28C5F-FDBF-9A46-9F27-14F8E8FE9680}"/>
+    <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{3CC28C5F-FDBF-9A46-9F27-14F8E8FE9680}"/>
   </bookViews>
   <sheets>
     <sheet name="Warm Up" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="74">
   <si>
     <t>N°</t>
   </si>
@@ -211,24 +211,6 @@
     <t>Wall Crawl</t>
   </si>
   <si>
-    <t>Trazioni Massimali</t>
-  </si>
-  <si>
-    <t>Dumbell Front Raises</t>
-  </si>
-  <si>
-    <t>AUMENTA CARICO OGNI 3-4 SESSIONI</t>
-  </si>
-  <si>
-    <t>Porta il braccio a 90°</t>
-  </si>
-  <si>
-    <t>Dumbell Reverse Files</t>
-  </si>
-  <si>
-    <t>Shoulder Shrugs</t>
-  </si>
-  <si>
     <t>TRAINING 1</t>
   </si>
   <si>
@@ -283,39 +265,44 @@
     <t>[Finger Lift] Full Crimp @10mm</t>
   </si>
   <si>
-    <t>Scegli prese vicine tra loro e dure per scalare statico e controllato. Stai 4-7" su ciascuna presa, prima di muovere la mano (piedi liberi).
+    <t>Scegli prese vicine tra loro e dure per scalare statico e controllato. Stai 4-7" su ciascuna presa, prima di muovere la mano (piedi liberi). Prese sempre in posizioni vicine al corpo, per non irritare la spalla.
 8-10 movimenti in 45-60". (L’inclinazione del pannello sceglila in base a quale ti consente di muoverti in questo modo)</t>
   </si>
   <si>
-    <t>eventualmente aggiusta carico</t>
-  </si>
-  <si>
-    <t>10 max-in-a-day</t>
-  </si>
-  <si>
-    <t>Voglio che in una sessione chiudi almeno 6 blocchi di 6a+ prima di provare i 6b. Questo ti costringerà a scalare tutti i blocchi presenti, anche negli stili che ti piacciono meno</t>
-  </si>
-  <si>
-    <t>Devi chiudere 10 blocchi in una sessione. Parti dal grado più basso presente al Moonboard, secondo la sua gradazione, e non puoi passare al grado successivo finchè non hai chiuso almeno 6 blocchi del grado precedente in una singola sessione.
-3 tentativi per il singolo blocco al massimo, poi passa al successivo se non lo riesci a chiudere. Quando in una sessione riesci a fare 6 6a+ puoi iniziare a provare i 6b, e così via verso l'alto.</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Limit Bouldering</t>
-  </si>
-  <si>
-    <t>3-4</t>
-  </si>
-  <si>
-    <t>85% massimale</t>
-  </si>
-  <si>
-    <t>Seleziona dei blocchi che siano fuori dalla tua zona di fattibilità, al Moonboard oppure sul muro boulder della palestra. Virtualmente vorrei blocchi che non riuscirai a fare per svariate sessioni. L’idea di fondo è di provare sequenze di 2-3 movimenti, che richiedano il 100% di quello che hai per star attaccato. Riposi ampi tra i tentativi, per conservare la potenza (che è il senso dell’esercizio). Lavora 1 grado sopra il grado massimo scalato al Moon fin’ora o nella tua palestra. Vorrei che tenessi questa sessione breve, e puntare tutto sulla qualità della stessa. Idealmente selezionerei 3-4 blocchi-progetto, e spenderei 20-30’ su ciascuno, riposando 1-2’ tra le sequenze di movimenti, e 5’ tra i blocchi. Cerca di prestarci attenzione, e sviluppare il feeling per questa cosa: quando inizi a sentire le prese meno bene, essere meno dinamico, più lento, lì è dove interrompere. In questo esercizio dovrebbe essere più facile da intuire, per via della sua intensità.</t>
-  </si>
-  <si>
-    <t>20-30'</t>
+    <t>Elevazione con manubrio</t>
+  </si>
+  <si>
+    <t>ripetizioni lente</t>
+  </si>
+  <si>
+    <t>Panca piana isometrica</t>
+  </si>
+  <si>
+    <t>Trova il carico che riesci a mantenere nella posizione con gomiti a 90° per circa 30’’.</t>
+  </si>
+  <si>
+    <t>Rotazione esterna sul fianco</t>
+  </si>
+  <si>
+    <t>Rematore con manubrio</t>
+  </si>
+  <si>
+    <t>Se preferisci puoi farlo con il bilanciere oppure il pullery ai cavi.</t>
+  </si>
+  <si>
+    <t>Dumbell drag plank</t>
+  </si>
+  <si>
+    <t>Downward dog toe taps</t>
+  </si>
+  <si>
+    <t>Parti con 20’’ e un peso che senti di poter gestire bene e datti come obiettivo quello di aumentare di 3’’ a settimana.</t>
+  </si>
+  <si>
+    <t>Datti come obiettivo quello di aumentare di 3’’ a settimana.</t>
+  </si>
+  <si>
+    <t>Esegu l’esercizio come mostrato nel video, per 30’’.</t>
   </si>
 </sst>
 </file>
@@ -542,7 +529,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -616,9 +603,6 @@
     <xf numFmtId="1" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -631,9 +615,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -641,17 +622,11 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -676,15 +651,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -709,8 +675,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1062,15 +1031,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -1332,17 +1301,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -1471,7 +1440,7 @@
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.125" customWidth="1"/>
@@ -1481,17 +1450,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="50" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
+      <c r="A1" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -1524,10 +1493,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C3" s="19">
         <v>3</v>
@@ -1553,10 +1522,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C4" s="19">
         <v>2</v>
@@ -1582,10 +1551,10 @@
     </row>
     <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A5" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C5" s="19">
         <v>2</v>
@@ -1611,155 +1580,180 @@
     </row>
     <row r="6" spans="1:9" ht="57" x14ac:dyDescent="0.25">
       <c r="A6" s="24">
-        <v>5</v>
-      </c>
-      <c r="B6" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="28" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="24">
         <v>3</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27">
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="26">
         <v>240</v>
       </c>
-      <c r="H6" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="28" t="s">
+      <c r="H6" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="30">
+        <v>5</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="30">
+        <v>3</v>
+      </c>
+      <c r="D7" s="30">
+        <v>10</v>
+      </c>
+      <c r="E7" s="30">
+        <v>2</v>
+      </c>
+      <c r="F7" s="30">
+        <v>12</v>
+      </c>
+      <c r="G7" s="30">
+        <v>120</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="32"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="30">
+        <v>6</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="30">
+        <v>4</v>
+      </c>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="30">
+        <v>120</v>
+      </c>
+      <c r="H8" s="31"/>
+      <c r="I8" s="32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="30">
+        <v>7</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="30">
+        <v>3</v>
+      </c>
+      <c r="D9" s="30">
+        <v>10</v>
+      </c>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="30">
+        <v>120</v>
+      </c>
+      <c r="H9" s="31"/>
+      <c r="I9" s="32"/>
+    </row>
+    <row r="10" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="30">
+        <v>8</v>
+      </c>
+      <c r="B10" s="49" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="142.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="24">
-        <v>7</v>
-      </c>
-      <c r="B7" s="56" t="s">
+      <c r="C10" s="30">
+        <v>3</v>
+      </c>
+      <c r="D10" s="30">
+        <v>8</v>
+      </c>
+      <c r="E10" s="30">
+        <v>2</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="30">
+        <v>120</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="32"/>
+    </row>
+    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="30">
+        <v>9</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="30">
+        <v>4</v>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30">
+        <v>2</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="30">
+        <v>120</v>
+      </c>
+      <c r="H11" s="31"/>
+      <c r="I11" s="32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="30">
+        <v>10</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="30">
+        <v>3</v>
+      </c>
+      <c r="D12" s="30">
+        <v>8</v>
+      </c>
+      <c r="E12" s="30">
+        <v>2</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="30">
+        <v>120</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="46"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="27">
-        <v>300</v>
-      </c>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
-        <v>8</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="32">
-        <v>5</v>
-      </c>
-      <c r="D8" s="32">
-        <v>4</v>
-      </c>
-      <c r="E8" s="32">
-        <v>2</v>
-      </c>
-      <c r="F8" s="32">
-        <v>12</v>
-      </c>
-      <c r="G8" s="32">
-        <v>240</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="32">
-        <v>9</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="32">
-        <v>3</v>
-      </c>
-      <c r="D9" s="32">
-        <v>10</v>
-      </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="32">
-        <v>120</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
-        <v>10</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="32">
-        <v>3</v>
-      </c>
-      <c r="D10" s="32">
-        <v>10</v>
-      </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="32">
-        <v>120</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="35"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="32">
-        <v>11</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="32">
-        <v>3</v>
-      </c>
-      <c r="D11" s="32">
-        <v>10</v>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="32">
-        <v>120</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1769,12 +1763,16 @@
     <hyperlink ref="B3" r:id="rId1" display="[Finger Lift] 4 fingers" xr:uid="{314C9D08-E561-8245-8C1F-B2EC06CE198D}"/>
     <hyperlink ref="B4" r:id="rId2" display="[Finger Lift] Front 3 Drag" xr:uid="{CFB0B7CF-3812-4C40-AD6C-4A465837FAC9}"/>
     <hyperlink ref="B5" r:id="rId3" display="[Finger Lift] Full Crimp" xr:uid="{DB7E17DA-75C3-8643-BCFD-584AECF07BD1}"/>
-    <hyperlink ref="B9" r:id="rId4" xr:uid="{10BD12D2-FCA6-1845-B804-153C82C280EF}"/>
-    <hyperlink ref="B10" r:id="rId5" xr:uid="{029B8290-BBE7-924D-AC14-DEE05D07F349}"/>
-    <hyperlink ref="B6" r:id="rId6" display="Wall Crawl Warm Up" xr:uid="{4B2B7B91-2549-4EA6-987F-27908CF6FF6C}"/>
-    <hyperlink ref="B7" r:id="rId7" xr:uid="{18E07A82-9C7F-4C36-901C-7D82C559BE70}"/>
+    <hyperlink ref="B6" r:id="rId4" display="Wall Crawl Warm Up" xr:uid="{4B2B7B91-2549-4EA6-987F-27908CF6FF6C}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{A7172EA4-513B-4485-B0C7-8703753C9CF3}"/>
+    <hyperlink ref="B8" r:id="rId6" xr:uid="{C7002C6C-104C-4157-9F4E-8C508D643134}"/>
+    <hyperlink ref="B9" r:id="rId7" xr:uid="{E501E4D2-68F1-4653-8D4D-BA8915F32C8D}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{A0135D70-54CA-4D5D-B747-631E4A4C8B16}"/>
+    <hyperlink ref="B11" r:id="rId9" xr:uid="{9B0CB63F-25AB-46A3-986E-7281F76CAF00}"/>
+    <hyperlink ref="B12" r:id="rId10" xr:uid="{7428BB38-E41C-4129-9327-EA3DD9489F0E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
 </worksheet>
 </file>
 
@@ -1783,7 +1781,7 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.125" customWidth="1"/>
@@ -1793,17 +1791,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
+      <c r="A1" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -1835,257 +1833,170 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="19">
-        <v>2</v>
-      </c>
-      <c r="B3" s="20" t="s">
+      <c r="A3" s="30">
+        <v>1</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="30">
+        <v>3</v>
+      </c>
+      <c r="D3" s="30">
+        <v>10</v>
+      </c>
+      <c r="E3" s="30">
+        <v>2</v>
+      </c>
+      <c r="F3" s="30">
+        <v>12</v>
+      </c>
+      <c r="G3" s="30">
+        <v>120</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" s="32"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="30">
+        <v>2</v>
+      </c>
+      <c r="B4" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C4" s="30">
+        <v>4</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="30">
+        <v>120</v>
+      </c>
+      <c r="H4" s="31"/>
+      <c r="I4" s="32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="30">
         <v>3</v>
       </c>
-      <c r="D3" s="21">
+      <c r="B5" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="30">
+        <v>3</v>
+      </c>
+      <c r="D5" s="30">
+        <v>10</v>
+      </c>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="30">
+        <v>120</v>
+      </c>
+      <c r="H5" s="31"/>
+      <c r="I5" s="32"/>
+    </row>
+    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
         <v>4</v>
       </c>
-      <c r="E3" s="19">
-        <v>1</v>
-      </c>
-      <c r="F3" s="21" t="s">
+      <c r="B6" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="30">
+        <v>3</v>
+      </c>
+      <c r="D6" s="30">
+        <v>8</v>
+      </c>
+      <c r="E6" s="30">
+        <v>2</v>
+      </c>
+      <c r="F6" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="19">
-        <v>180</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="23" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="19">
+      <c r="G6" s="30">
+        <v>120</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="32"/>
+    </row>
+    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="30">
+        <v>5</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="30">
+        <v>4</v>
+      </c>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30">
+        <v>2</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="30">
+        <v>120</v>
+      </c>
+      <c r="H7" s="31"/>
+      <c r="I7" s="32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="30">
+        <v>6</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="30">
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="19">
-        <v>2</v>
-      </c>
-      <c r="D4" s="21">
-        <v>4</v>
-      </c>
-      <c r="E4" s="19">
-        <v>1</v>
-      </c>
-      <c r="F4" s="21" t="s">
+      <c r="D8" s="30">
+        <v>8</v>
+      </c>
+      <c r="E8" s="30">
+        <v>2</v>
+      </c>
+      <c r="F8" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="19">
-        <v>180</v>
-      </c>
-      <c r="H4" s="22" t="s">
-        <v>38</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
-        <v>4</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="19">
-        <v>2</v>
-      </c>
-      <c r="D5" s="21">
-        <v>4</v>
-      </c>
-      <c r="E5" s="19">
-        <v>1</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="19">
-        <v>180</v>
-      </c>
-      <c r="H5" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="57" x14ac:dyDescent="0.25">
-      <c r="A6" s="24">
-        <v>5</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="24">
-        <v>3</v>
-      </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27">
-        <v>240</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="71.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="24">
-        <v>6</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="30" t="s">
+      <c r="G8" s="30">
+        <v>120</v>
+      </c>
+      <c r="H8" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="D7" s="47">
-        <v>3</v>
-      </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="27">
-        <v>300</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="32">
-        <v>9</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="32">
-        <v>5</v>
-      </c>
-      <c r="D8" s="32">
-        <v>4</v>
-      </c>
-      <c r="E8" s="32">
-        <v>2</v>
-      </c>
-      <c r="F8" s="32">
-        <v>12</v>
-      </c>
-      <c r="G8" s="32">
-        <v>240</v>
-      </c>
-      <c r="H8" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="32">
-        <v>10</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="32">
-        <v>3</v>
-      </c>
-      <c r="D9" s="32">
-        <v>10</v>
-      </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="32">
-        <v>120</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32">
-        <v>11</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="32">
-        <v>3</v>
-      </c>
-      <c r="D10" s="32">
-        <v>10</v>
-      </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="32">
-        <v>120</v>
-      </c>
-      <c r="H10" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="I10" s="35"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="32">
-        <v>12</v>
-      </c>
-      <c r="B11" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="32">
-        <v>3</v>
-      </c>
-      <c r="D11" s="32">
-        <v>10</v>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="32">
-        <v>120</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="I11" s="35"/>
+      <c r="I8" s="32" t="s">
+        <v>73</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" display="[Finger Lift] 4 fingers" xr:uid="{F5E0BD4D-8E7B-4942-809D-AE8512E8AED3}"/>
-    <hyperlink ref="B4" r:id="rId2" display="[Finger Lift] Front 3 Drag" xr:uid="{90BBD89E-68AF-B449-8245-DF1A19856ACE}"/>
-    <hyperlink ref="B5" r:id="rId3" display="[Finger Lift] Full Crimp" xr:uid="{ADC63D58-CC2C-DF4B-80A5-566596A44057}"/>
-    <hyperlink ref="B6" r:id="rId4" display="Wall Crawl Warm Up" xr:uid="{A35276CC-9195-4045-9259-B080CC6C3587}"/>
-    <hyperlink ref="B9" r:id="rId5" xr:uid="{0E920E7C-7718-4A4C-B757-1D76CDEED9B6}"/>
-    <hyperlink ref="B10" r:id="rId6" xr:uid="{8A6637D6-208E-4EEB-BA1F-A6457C5E6DA5}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{89F4BB49-DB49-458B-9DBA-CE4EF135638D}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{2F5559C3-29F9-456D-AED7-88D4E2629AD9}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{B54B7C7C-F77C-4201-A2C3-224F6A87E6C3}"/>
+    <hyperlink ref="B6" r:id="rId4" xr:uid="{93D167B8-66FC-4C6E-8584-9B49BEB15022}"/>
+    <hyperlink ref="B7" r:id="rId5" xr:uid="{6FFCE2E3-58D7-408C-AF56-106AC147062C}"/>
+    <hyperlink ref="B8" r:id="rId6" xr:uid="{3747A92C-41A1-4338-B374-2FEFD6778307}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2111,17 +2022,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="A1" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -2157,7 +2068,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C3" s="7">
         <v>1</v>
@@ -2168,9 +2079,9 @@
       <c r="E3" s="7"/>
       <c r="F3" s="8"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37" t="s">
-        <v>54</v>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -2178,7 +2089,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
@@ -2189,11 +2100,11 @@
       <c r="E4" s="7"/>
       <c r="F4" s="8"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="I4" s="37" t="s">
-        <v>57</v>
+      <c r="H4" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -2201,7 +2112,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
@@ -2212,17 +2123,17 @@
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="I5" s="37"/>
+      <c r="H5" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="33"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
@@ -2233,17 +2144,17 @@
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" s="37"/>
+      <c r="H6" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="33"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C7" s="7">
         <v>2</v>
@@ -2256,64 +2167,64 @@
       <c r="G7" s="7">
         <v>60</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37" t="s">
-        <v>61</v>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="38">
+      <c r="A8" s="34">
         <v>6</v>
       </c>
-      <c r="B8" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="38">
-        <v>2</v>
-      </c>
-      <c r="D8" s="38">
+      <c r="B8" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="34">
+        <v>2</v>
+      </c>
+      <c r="D8" s="34">
         <v>15</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="38">
+      <c r="E8" s="34"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="34">
         <v>60</v>
       </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
     </row>
     <row r="9" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="55"/>
+      <c r="A9" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="48"/>
     </row>
     <row r="10" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="41">
+      <c r="A10" s="37">
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" s="41">
-        <v>1</v>
-      </c>
-      <c r="D10" s="41">
-        <v>2</v>
-      </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43" t="s">
-        <v>54</v>
+        <v>47</v>
+      </c>
+      <c r="C10" s="37">
+        <v>1</v>
+      </c>
+      <c r="D10" s="37">
+        <v>2</v>
+      </c>
+      <c r="E10" s="37"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="39" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -2321,7 +2232,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -2332,11 +2243,11 @@
       <c r="E11" s="7"/>
       <c r="F11" s="8"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>57</v>
+      <c r="H11" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -2344,7 +2255,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
@@ -2355,17 +2266,17 @@
       <c r="E12" s="7"/>
       <c r="F12" s="8"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="I12" s="37"/>
+      <c r="H12" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I12" s="33"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -2376,17 +2287,17 @@
       <c r="E13" s="7"/>
       <c r="F13" s="8"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="I13" s="37"/>
+      <c r="H13" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I13" s="33"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C14" s="7">
         <v>2</v>
@@ -2399,64 +2310,64 @@
       <c r="G14" s="7">
         <v>60</v>
       </c>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37" t="s">
-        <v>61</v>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="38">
+      <c r="A15" s="34">
         <v>12</v>
       </c>
-      <c r="B15" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="38">
-        <v>2</v>
-      </c>
-      <c r="D15" s="38">
+      <c r="B15" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="34">
+        <v>2</v>
+      </c>
+      <c r="D15" s="34">
         <v>15</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="38">
+      <c r="E15" s="34"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="34">
         <v>60</v>
       </c>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
     </row>
     <row r="16" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="55"/>
+      <c r="A16" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="48"/>
     </row>
     <row r="17" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="41">
+      <c r="A17" s="37">
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="41">
-        <v>1</v>
-      </c>
-      <c r="D17" s="41">
-        <v>2</v>
-      </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43" t="s">
-        <v>54</v>
+        <v>47</v>
+      </c>
+      <c r="C17" s="37">
+        <v>1</v>
+      </c>
+      <c r="D17" s="37">
+        <v>2</v>
+      </c>
+      <c r="E17" s="37"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -2464,7 +2375,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C18" s="7">
         <v>1</v>
@@ -2475,11 +2386,11 @@
       <c r="E18" s="7"/>
       <c r="F18" s="8"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>57</v>
+      <c r="H18" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I18" s="33" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -2487,7 +2398,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -2498,17 +2409,17 @@
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" s="37"/>
+      <c r="H19" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="33"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C20" s="7">
         <v>1</v>
@@ -2519,17 +2430,17 @@
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="I20" s="37"/>
+      <c r="H20" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="33"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>17</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C21" s="7">
         <v>2</v>
@@ -2542,17 +2453,17 @@
       <c r="G21" s="7">
         <v>60</v>
       </c>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37" t="s">
-        <v>61</v>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>18</v>
       </c>
-      <c r="B22" s="44" t="s">
-        <v>62</v>
+      <c r="B22" s="40" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="7">
         <v>2</v>
@@ -2565,8 +2476,8 @@
       <c r="G22" s="7">
         <v>60</v>
       </c>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/public/fisiorock_block3.xlsx
+++ b/public/fisiorock_block3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U82739\workspace\fisiorock-workouts\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA83248-7C4D-4BF4-A968-38D896548B1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5BEE93-7D16-461B-905D-A1AA40A28F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="0" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{3CC28C5F-FDBF-9A46-9F27-14F8E8FE9680}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="74">
   <si>
     <t>N°</t>
   </si>
@@ -651,6 +651,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -674,12 +680,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1031,15 +1031,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
     </row>
     <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -1301,17 +1301,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -1450,17 +1450,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -1605,7 +1605,7 @@
       <c r="A7" s="30">
         <v>5</v>
       </c>
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="41" t="s">
         <v>62</v>
       </c>
       <c r="C7" s="30">
@@ -1632,7 +1632,7 @@
       <c r="A8" s="30">
         <v>6</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="41" t="s">
         <v>64</v>
       </c>
       <c r="C8" s="30">
@@ -1655,7 +1655,7 @@
       <c r="A9" s="30">
         <v>7</v>
       </c>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="41" t="s">
         <v>66</v>
       </c>
       <c r="C9" s="30">
@@ -1678,7 +1678,7 @@
       <c r="A10" s="30">
         <v>8</v>
       </c>
-      <c r="B10" s="49" t="s">
+      <c r="B10" s="41" t="s">
         <v>67</v>
       </c>
       <c r="C10" s="30">
@@ -1705,7 +1705,7 @@
       <c r="A11" s="30">
         <v>9</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="42" t="s">
         <v>69</v>
       </c>
       <c r="C11" s="30">
@@ -1730,7 +1730,7 @@
       <c r="A12" s="30">
         <v>10</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="42" t="s">
         <v>70</v>
       </c>
       <c r="C12" s="30">
@@ -1781,7 +1781,7 @@
   <sheetPr>
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.125" customWidth="1"/>
@@ -1791,17 +1791,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -1833,119 +1833,131 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="30">
-        <v>1</v>
-      </c>
-      <c r="B3" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="C3" s="30">
+      <c r="A3" s="19">
+        <v>1</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="19">
         <v>3</v>
       </c>
-      <c r="D3" s="30">
-        <v>10</v>
-      </c>
-      <c r="E3" s="30">
-        <v>2</v>
-      </c>
-      <c r="F3" s="30">
-        <v>12</v>
-      </c>
-      <c r="G3" s="30">
-        <v>120</v>
-      </c>
-      <c r="H3" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="32"/>
+      <c r="D3" s="21">
+        <v>4</v>
+      </c>
+      <c r="E3" s="19">
+        <v>1</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="19">
+        <v>180</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="30">
-        <v>2</v>
-      </c>
-      <c r="B4" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="30">
+      <c r="A4" s="19">
+        <v>2</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="19">
+        <v>2</v>
+      </c>
+      <c r="D4" s="21">
         <v>4</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30" t="s">
+      <c r="E4" s="19">
+        <v>1</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="30">
-        <v>120</v>
-      </c>
-      <c r="H4" s="31"/>
-      <c r="I4" s="32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="30">
+      <c r="G4" s="19">
+        <v>180</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" s="30">
-        <v>3</v>
-      </c>
-      <c r="D5" s="30">
-        <v>10</v>
-      </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30" t="s">
+      <c r="B5" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="19">
+        <v>2</v>
+      </c>
+      <c r="D5" s="21">
+        <v>4</v>
+      </c>
+      <c r="E5" s="19">
+        <v>1</v>
+      </c>
+      <c r="F5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="30">
-        <v>120</v>
-      </c>
-      <c r="H5" s="31"/>
-      <c r="I5" s="32"/>
-    </row>
-    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="G5" s="19">
+        <v>180</v>
+      </c>
+      <c r="H5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>4</v>
       </c>
-      <c r="B6" s="49" t="s">
-        <v>67</v>
+      <c r="B6" s="41" t="s">
+        <v>62</v>
       </c>
       <c r="C6" s="30">
         <v>3</v>
       </c>
       <c r="D6" s="30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" s="30">
         <v>2</v>
       </c>
-      <c r="F6" s="30" t="s">
-        <v>32</v>
+      <c r="F6" s="30">
+        <v>12</v>
       </c>
       <c r="G6" s="30">
         <v>120</v>
       </c>
       <c r="H6" s="31" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="I6" s="32"/>
     </row>
-    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>5</v>
       </c>
-      <c r="B7" s="50" t="s">
-        <v>69</v>
+      <c r="B7" s="41" t="s">
+        <v>64</v>
       </c>
       <c r="C7" s="30">
         <v>4</v>
       </c>
       <c r="D7" s="30"/>
-      <c r="E7" s="30">
-        <v>2</v>
-      </c>
+      <c r="E7" s="30"/>
       <c r="F7" s="30" t="s">
         <v>32</v>
       </c>
@@ -1954,35 +1966,110 @@
       </c>
       <c r="H7" s="31"/>
       <c r="I7" s="32" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="30">
         <v>6</v>
       </c>
-      <c r="B8" s="50" t="s">
-        <v>70</v>
+      <c r="B8" s="41" t="s">
+        <v>66</v>
       </c>
       <c r="C8" s="30">
         <v>3</v>
       </c>
       <c r="D8" s="30">
-        <v>8</v>
-      </c>
-      <c r="E8" s="30">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E8" s="30"/>
       <c r="F8" s="30" t="s">
         <v>32</v>
       </c>
       <c r="G8" s="30">
         <v>120</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="31"/>
+      <c r="I8" s="32"/>
+    </row>
+    <row r="9" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="30">
+        <v>7</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="30">
+        <v>3</v>
+      </c>
+      <c r="D9" s="30">
+        <v>8</v>
+      </c>
+      <c r="E9" s="30">
+        <v>2</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="30">
+        <v>120</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="32"/>
+    </row>
+    <row r="10" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="30">
+        <v>8</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="30">
+        <v>4</v>
+      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30">
+        <v>2</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="30">
+        <v>120</v>
+      </c>
+      <c r="H10" s="31"/>
+      <c r="I10" s="32" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="30">
+        <v>9</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="30">
+        <v>3</v>
+      </c>
+      <c r="D11" s="30">
+        <v>8</v>
+      </c>
+      <c r="E11" s="30">
+        <v>2</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" s="30">
+        <v>120</v>
+      </c>
+      <c r="H11" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I11" s="32" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1991,12 +2078,15 @@
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{89F4BB49-DB49-458B-9DBA-CE4EF135638D}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{2F5559C3-29F9-456D-AED7-88D4E2629AD9}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{B54B7C7C-F77C-4201-A2C3-224F6A87E6C3}"/>
-    <hyperlink ref="B6" r:id="rId4" xr:uid="{93D167B8-66FC-4C6E-8584-9B49BEB15022}"/>
-    <hyperlink ref="B7" r:id="rId5" xr:uid="{6FFCE2E3-58D7-408C-AF56-106AC147062C}"/>
-    <hyperlink ref="B8" r:id="rId6" xr:uid="{3747A92C-41A1-4338-B374-2FEFD6778307}"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{89F4BB49-DB49-458B-9DBA-CE4EF135638D}"/>
+    <hyperlink ref="B7" r:id="rId2" xr:uid="{2F5559C3-29F9-456D-AED7-88D4E2629AD9}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{B54B7C7C-F77C-4201-A2C3-224F6A87E6C3}"/>
+    <hyperlink ref="B9" r:id="rId4" xr:uid="{93D167B8-66FC-4C6E-8584-9B49BEB15022}"/>
+    <hyperlink ref="B10" r:id="rId5" xr:uid="{6FFCE2E3-58D7-408C-AF56-106AC147062C}"/>
+    <hyperlink ref="B11" r:id="rId6" xr:uid="{3747A92C-41A1-4338-B374-2FEFD6778307}"/>
+    <hyperlink ref="B3" r:id="rId7" display="[Finger Lift] 4 fingers" xr:uid="{10DDE890-1DAF-42FB-9258-1A76F068E499}"/>
+    <hyperlink ref="B4" r:id="rId8" display="[Finger Lift] Front 3 Drag" xr:uid="{2C806D19-E4E6-43C1-A48F-C51B759058FD}"/>
+    <hyperlink ref="B5" r:id="rId9" display="[Finger Lift] Full Crimp" xr:uid="{34F94862-3D75-4F6D-B0A2-7E8B4135867F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2022,17 +2112,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -2194,17 +2284,17 @@
       <c r="I8" s="36"/>
     </row>
     <row r="9" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="46" t="s">
+      <c r="A9" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="48"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="50"/>
     </row>
     <row r="10" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
@@ -2337,17 +2427,17 @@
       <c r="I15" s="36"/>
     </row>
     <row r="16" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="50"/>
     </row>
     <row r="17" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
